--- a/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/CN/Dialog/Drama/Vajra.xlsx
+++ b/GranBlueFantasy_And_OtherCygame_Support_Dll/package/LangMod/CN/Dialog/Drama/Vajra.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="237">
   <si>
     <t>step</t>
   </si>
@@ -180,13 +180,13 @@
     <t>choice</t>
   </si>
   <si>
-    <t>*雑談*</t>
-  </si>
-  <si>
-    <t>*Chat*</t>
-  </si>
-  <si>
-    <t>*闲聊*</t>
+    <t>*雑談/招待*</t>
+  </si>
+  <si>
+    <t>*Chat/Invite*</t>
+  </si>
+  <si>
+    <t>*闲聊/邀请*</t>
   </si>
   <si>
     <t>Vajra_mission</t>
@@ -213,16 +213,16 @@
     <t>*切磋*</t>
   </si>
   <si>
-    <t>_investShop</t>
-  </si>
-  <si>
-    <t>*投資*</t>
-  </si>
-  <si>
-    <t>*Invest*</t>
-  </si>
-  <si>
-    <t>*投资*</t>
+    <t>Vajra_Shop</t>
+  </si>
+  <si>
+    <t>*店*</t>
+  </si>
+  <si>
+    <t>*Shop*</t>
+  </si>
+  <si>
+    <t>*商店*</t>
   </si>
   <si>
     <t>_heal</t>
@@ -237,7 +237,16 @@
     <t>*治疗*</t>
   </si>
   <si>
-    <t>choice/buy</t>
+    <t>_daMakeMaid</t>
+  </si>
+  <si>
+    <t>メイドに設定する</t>
+  </si>
+  <si>
+    <t>Set as a maid</t>
+  </si>
+  <si>
+    <t>设置为女仆</t>
   </si>
   <si>
     <t>choice/bye</t>
@@ -271,6 +280,30 @@
   </si>
   <si>
     <t>有新情报吗？</t>
+  </si>
+  <si>
+    <t>Vajra_joinParty</t>
+  </si>
+  <si>
+    <t>パーティーを招待する</t>
+  </si>
+  <si>
+    <t>Invite your party</t>
+  </si>
+  <si>
+    <t>加入队伍</t>
+  </si>
+  <si>
+    <t>_leaveParty</t>
+  </si>
+  <si>
+    <t>パーティーを離脱する</t>
+  </si>
+  <si>
+    <t>Leave your party</t>
+  </si>
+  <si>
+    <t>离开队伍</t>
   </si>
   <si>
     <t>団長、そんなに暇なら手伝ってくれませんか？</t>
@@ -685,6 +718,9 @@
     <t>是你呀，你找到他了吗？</t>
   </si>
   <si>
+    <t>choice/buy</t>
+  </si>
+  <si>
     <t>Vajra_InPartyMission_2</t>
   </si>
   <si>
@@ -901,6 +937,27 @@
   </si>
   <si>
     <t>不用感谢。</t>
+  </si>
+  <si>
+    <t>何かお買いものをお考えですか？团長。</t>
+  </si>
+  <si>
+    <t>Do you want to buy something, Captain.</t>
+  </si>
+  <si>
+    <t>你想要买些什么吗？团长。</t>
+  </si>
+  <si>
+    <t>_investShop</t>
+  </si>
+  <si>
+    <t>*投資*</t>
+  </si>
+  <si>
+    <t>*Invest*</t>
+  </si>
+  <si>
+    <t>*投资*</t>
   </si>
 </sst>
 </file>
@@ -2179,7 +2236,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N140"/>
   <sheetFormatPr defaultColWidth="7.33333333333333" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="25" style="4" customWidth="1"/>
@@ -2238,8 +2295,8 @@
     </row>
     <row r="2" spans="1:13">
       <c r="I2" s="4">
-        <f>MAX(I5:I1048364)</f>
-        <v>51</v>
+        <f>MAX(I5:I1048369)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2450,32 +2507,50 @@
       </c>
     </row>
     <row r="22" spans="1:13">
+      <c r="B22" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="E22" s="10" t="s">
-        <v>49</v>
+        <v>29</v>
+      </c>
+      <c r="I22" s="4">
+        <v>56</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="E23" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" spans="1:13">
       <c r="B24" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1"/>
     <row r="26" spans="1:13">
       <c r="A26" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="B27" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>17</v>
@@ -2495,21 +2570,21 @@
         <v>4</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="B32" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>29</v>
@@ -2518,326 +2593,332 @@
         <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:13">
+      <c r="B33" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="E33" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="B34" s="9" t="s">
-        <v>51</v>
+        <v>29</v>
+      </c>
+      <c r="I33" s="4">
+        <v>52</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:13">
+      <c r="B34" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1"/>
+        <v>29</v>
+      </c>
+      <c r="I34" s="4">
+        <v>53</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:13">
+      <c r="E35" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="6" t="s">
+      <c r="B36" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1"/>
+    <row r="38" spans="1:13">
+      <c r="A38" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
-      <c r="G37" s="4" t="s">
+    <row r="39" spans="1:13">
+      <c r="G39" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I39" s="4">
         <v>5</v>
       </c>
-      <c r="J37" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:13">
-      <c r="E38" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
-      <c r="B39" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1"/>
+      <c r="J39" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:13">
+      <c r="E40" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="41" spans="1:13">
-      <c r="A41" s="6" t="s">
+      <c r="B41" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1"/>
+    <row r="43" spans="1:13">
+      <c r="A43" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
-      <c r="B42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:13">
-      <c r="B43" s="5" t="s">
+    <row r="44" spans="1:13">
+      <c r="B44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:13">
+      <c r="B45" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:13">
-      <c r="G44" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I44" s="4">
-        <v>6</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+      <c r="E45" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="G45" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I45" s="4">
-        <v>7</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" ht="17.25" spans="1:13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:13">
       <c r="G46" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I46" s="4">
+        <v>6</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="G47" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="4">
+        <v>7</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" spans="1:13">
+      <c r="G48" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="4">
         <v>8</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="M46" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="B48" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I48" s="4">
-        <v>9</v>
-      </c>
       <c r="J48" s="4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
-      <c r="B49" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I49" s="4">
-        <v>10</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="B50" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>29</v>
       </c>
       <c r="I50" s="4">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:13">
-      <c r="B51" s="9" t="s">
-        <v>51</v>
+      <c r="B51" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>29</v>
       </c>
       <c r="I51" s="4">
+        <v>10</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="B52" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="4">
+        <v>11</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="B53" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I53" s="4">
         <v>12</v>
       </c>
-      <c r="J51" s="4" t="s">
+      <c r="J53" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1"/>
+    <row r="55" spans="1:13">
+      <c r="A55" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="K51" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1"/>
-    <row r="53" spans="1:13">
-      <c r="A53" s="6" t="s">
+    </row>
+    <row r="56" spans="1:13">
+      <c r="E56" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="G56" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
-      <c r="E54" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="E55" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
-      <c r="G56" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I56" s="4">
-        <v>13</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M56" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
     <row r="57" spans="1:13">
+      <c r="E57" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>104</v>
+      </c>
       <c r="G57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" s="4">
-        <v>14</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -2845,19 +2926,19 @@
         <v>20</v>
       </c>
       <c r="I58" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -2865,301 +2946,319 @@
         <v>20</v>
       </c>
       <c r="I59" s="4">
+        <v>14</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13">
+      <c r="G60" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="4">
+        <v>15</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13">
+      <c r="G61" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="4">
         <v>17</v>
       </c>
-      <c r="J59" s="4" t="s">
+      <c r="J61" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13">
+      <c r="B63" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63" s="4">
+        <v>16</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1"/>
+    <row r="65" spans="1:13">
+      <c r="A65" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13">
+      <c r="E66" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F66" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="K59" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="M59" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
-      <c r="B61" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I61" s="4">
-        <v>16</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="M61" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1"/>
-    <row r="63" spans="1:13">
-      <c r="A63" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
-      <c r="E64" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="5:13">
-      <c r="E65" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="66" spans="5:13">
-      <c r="E66" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>110</v>
-      </c>
       <c r="G66" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="5:13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13">
       <c r="E67" s="10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="5:13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13">
       <c r="E68" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>112</v>
+        <v>76</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>121</v>
       </c>
       <c r="G68" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13">
+      <c r="E69" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13">
+      <c r="E70" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="69" spans="5:13">
-      <c r="G69" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I69" s="4">
-        <v>18</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="M69" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="70" spans="5:13">
-      <c r="G70" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I70" s="4">
-        <v>19</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="M70" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="71" spans="5:13">
+    <row r="71" spans="1:13">
       <c r="G71" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I71" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72" spans="5:13">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13">
       <c r="G72" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I72" s="4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="73" spans="5:13">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13">
       <c r="G73" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I73" s="4">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="74" spans="5:13">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13">
       <c r="G74" s="4" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="I74" s="4">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M74" s="4" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="75" spans="5:13">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13">
       <c r="G75" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I75" s="4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="76" spans="5:13">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13">
+      <c r="G76" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="I76" s="4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="77" spans="5:13">
-      <c r="E77" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>137</v>
-      </c>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13">
       <c r="G77" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="78" spans="5:13">
-      <c r="E78" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="5:13">
+      <c r="I77" s="4">
+        <v>24</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13">
+      <c r="I78" s="4">
+        <v>25</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13">
       <c r="E79" s="10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="5:13">
+    <row r="80" spans="1:13">
       <c r="E80" s="10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>20</v>
@@ -3167,632 +3266,778 @@
     </row>
     <row r="81" spans="1:13">
       <c r="E81" s="10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="82" ht="12.75" customHeight="1" spans="1:13">
-      <c r="I82" s="4">
+    <row r="82" spans="1:13">
+      <c r="E82" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13">
+      <c r="E83" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" ht="12.75" customHeight="1" spans="1:13">
+      <c r="I84" s="4">
         <v>26</v>
       </c>
-      <c r="J82" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="L82" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="M82" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13">
-      <c r="B84" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E84" s="10" t="s">
+      <c r="J84" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13">
+      <c r="B86" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E86" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I84" s="4">
+      <c r="I86" s="4">
         <v>27</v>
       </c>
-      <c r="J84" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="K84" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="L84" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="M84" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1"/>
-    <row r="86" spans="1:13">
-      <c r="A86" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13">
-      <c r="G87" s="4" t="s">
+      <c r="J86" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1"/>
+    <row r="88" spans="1:13">
+      <c r="A88" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="G89" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I87" s="4">
+      <c r="I89" s="4">
         <v>28</v>
       </c>
-      <c r="J87" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="L87" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="M87" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="E89" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13">
-      <c r="B90" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E90" s="10" t="s">
+      <c r="J89" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13">
+      <c r="E91" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13">
+      <c r="B92" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E92" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I90" s="4">
+      <c r="F92" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I92" s="4">
         <v>33</v>
       </c>
-      <c r="J90" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="M90" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="B91" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E91" s="10" t="s">
+      <c r="J92" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13">
+      <c r="B93" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E93" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I91" s="4">
+      <c r="I93" s="4">
         <v>29</v>
       </c>
-      <c r="J91" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="L91" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="M91" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1"/>
-    <row r="93" spans="1:13">
-      <c r="A93" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13">
-      <c r="E94" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F94" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
+      <c r="J93" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1"/>
     <row r="95" spans="1:13">
-      <c r="E95" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F95" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>67</v>
+      <c r="A95" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="96" spans="1:13">
       <c r="E96" s="10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="97" spans="2:13">
       <c r="E97" s="10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13">
-      <c r="F98" s="7"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" spans="2:13">
+      <c r="E98" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F98" s="11" t="s">
+        <v>122</v>
+      </c>
       <c r="G98" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I98" s="4">
-        <v>34</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="M98" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="99" spans="2:13">
+      <c r="E99" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F99" s="11" t="s">
+        <v>171</v>
+      </c>
       <c r="G99" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I99" s="4">
-        <v>35</v>
-      </c>
-      <c r="J99" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="K99" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="M99" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13">
+    </row>
+    <row r="100" spans="2:13">
+      <c r="F100" s="7"/>
       <c r="G100" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I100" s="4">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="101" spans="2:13">
       <c r="G101" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I101" s="4">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="M101" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="102" spans="2:13">
       <c r="G102" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I102" s="4">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="103" spans="2:13">
       <c r="G103" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I103" s="4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="2:13">
       <c r="G104" s="4" t="s">
         <v>20</v>
       </c>
       <c r="I104" s="4">
+        <v>39</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M104" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="105" spans="2:13">
+      <c r="G105" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I105" s="4">
+        <v>40</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="106" spans="2:13">
+      <c r="G106" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I106" s="4">
         <v>41</v>
       </c>
-      <c r="J104" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="K104" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="M104" s="4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13">
-      <c r="I105" s="4">
+      <c r="J106" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M106" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="107" spans="2:13">
+      <c r="I107" s="4">
         <v>51</v>
       </c>
-      <c r="J105" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="K105" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="L105" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="M105" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13">
-      <c r="E106" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F106" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13">
-      <c r="E107" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F107" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13">
-      <c r="B109" s="16" t="s">
-        <v>51</v>
-      </c>
+      <c r="J107" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="M107" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="108" spans="2:13">
+      <c r="E108" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109" spans="2:13">
       <c r="E109" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I109" s="4">
-        <v>43</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="K109" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="L109" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="M109" s="4" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13">
-      <c r="B110" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I110" s="4">
-        <v>44</v>
-      </c>
-      <c r="J110" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="K110" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="L110" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="M110" s="4" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13">
-      <c r="B111" s="6" t="s">
-        <v>193</v>
+        <v>76</v>
+      </c>
+      <c r="F109" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111" spans="2:13">
+      <c r="B111" s="16" t="s">
+        <v>54</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>29</v>
       </c>
       <c r="I111" s="4">
+        <v>43</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="L111" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="M111" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="2:13">
+      <c r="B112" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I112" s="4">
+        <v>44</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M112" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
+      <c r="B113" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I113" s="4">
         <v>45</v>
       </c>
-      <c r="J111" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="K111" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="L111" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="M111" s="4" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="112" s="3" customFormat="1" spans="1:13">
-      <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
-      <c r="J112" s="1"/>
-      <c r="K112" s="1"/>
-      <c r="L112" s="1"/>
-      <c r="M112" s="1"/>
-    </row>
-    <row r="113" spans="1:14">
-      <c r="A113" s="6" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14">
-      <c r="E114" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F114" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="J113" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="M113" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="114" s="3" customFormat="1" spans="1:14">
+      <c r="A114" s="1"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
     </row>
     <row r="115" spans="1:14">
-      <c r="G115" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I115" s="4">
-        <v>46</v>
-      </c>
-      <c r="J115" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="K115" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="L115" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="M115" s="4" t="s">
+      <c r="A115" s="6" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="E116" s="10" t="s">
-        <v>65</v>
+        <v>209</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:14">
+      <c r="G117" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="I117" s="4">
+        <v>46</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="L117" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
+      <c r="E118" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F118" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
+      <c r="I119" s="4">
         <v>47</v>
       </c>
-      <c r="J117" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="K117" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="L117" s="4" t="s">
+      <c r="J119" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="K119" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="L119" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="120" ht="26.3" customHeight="1"/>
+    <row r="121" spans="1:14">
+      <c r="B121" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I121" s="4">
+        <v>48</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="L121" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="122" s="3" customFormat="1" spans="1:14">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="1"/>
+    </row>
+    <row r="123" spans="1:14">
+      <c r="A123" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="M117" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="118" ht="26.3" customHeight="1"/>
-    <row r="119" spans="1:14">
-      <c r="B119" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E119" s="10" t="s">
+    </row>
+    <row r="124" spans="1:14">
+      <c r="E124" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F124" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
+      <c r="G125" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I125" s="4">
+        <v>49</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="K125" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="L125" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="M125" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="N125" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
+      <c r="B127" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E127" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I119" s="4">
-        <v>48</v>
-      </c>
-      <c r="J119" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="K119" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="L119" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="M119" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="120" s="3" customFormat="1" spans="1:14">
-      <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
-      <c r="H120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1"/>
-      <c r="K120" s="1"/>
-      <c r="L120" s="1"/>
-      <c r="M120" s="1"/>
-    </row>
-    <row r="121" spans="1:14">
-      <c r="A121" s="6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14">
-      <c r="E122" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F122" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="G122" s="4" t="s">
+      <c r="I127" s="4">
+        <v>50</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="K127" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="L127" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="M127" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="128" s="3" customFormat="1" spans="1:14">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+      <c r="E128" s="1"/>
+      <c r="F128" s="1"/>
+      <c r="G128" s="1"/>
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+      <c r="J128" s="1"/>
+      <c r="K128" s="1"/>
+      <c r="L128" s="1"/>
+      <c r="M128" s="1"/>
+    </row>
+    <row r="129" spans="1:14">
+      <c r="A129" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14">
+      <c r="G130" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="123" spans="1:14">
-      <c r="G123" s="4" t="s">
+      <c r="I130" s="4">
+        <v>54</v>
+      </c>
+      <c r="J130" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="K130" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="L130" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="M130" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="N130" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="132" s="2" customFormat="1" spans="1:14">
+      <c r="B132" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132" s="14"/>
+      <c r="I132" s="4">
+        <v>55</v>
+      </c>
+      <c r="J132" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="K132" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L132" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="M132" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="133" customFormat="1" spans="1:14">
+      <c r="B133" s="4"/>
+      <c r="E133" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F133" s="4"/>
+      <c r="I133" s="4"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="4"/>
+      <c r="L133" s="4"/>
+      <c r="M133" s="4"/>
+    </row>
+    <row r="134" customFormat="1" spans="1:14">
+      <c r="B134" s="4"/>
+      <c r="E134" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F134" s="4"/>
+      <c r="I134" s="4"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
+      <c r="L134" s="4"/>
+      <c r="M134" s="4"/>
+    </row>
+    <row r="135" s="2" customFormat="1" spans="1:14">
+      <c r="B135" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="136" s="3" customFormat="1" spans="1:14">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+      <c r="E136" s="1"/>
+      <c r="F136" s="1"/>
+      <c r="G136" s="1"/>
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+      <c r="J136" s="1"/>
+      <c r="K136" s="1"/>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+    </row>
+    <row r="137" spans="1:14">
+      <c r="A137" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14">
+      <c r="E138" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G138" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I123" s="4">
-        <v>49</v>
-      </c>
-      <c r="J123" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="K123" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="L123" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="M123" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="N123" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="125" spans="1:14">
-      <c r="B125" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E125" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="I125" s="4">
-        <v>50</v>
-      </c>
-      <c r="J125" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="K125" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="L125" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="M125" s="4" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="126" s="3" customFormat="1" spans="1:14">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-    </row>
+    </row>
+    <row r="139" spans="1:14">
+      <c r="B139" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" s="1" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
